--- a/samples/ss_kediri12_ingest.xlsx
+++ b/samples/ss_kediri12_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,65 +535,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -632,24 +637,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,41 +691,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>NGORO7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>NGORO</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -752,30 +763,31 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR (bay 5 = MBL)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -808,34 +820,35 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>injeksi 150 kV Kediri</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -868,34 +881,35 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>T/L bay Kediri single phi</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -928,34 +942,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>150 kV Kertosono</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -988,30 +1003,31 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>60 MVA (bay 6,7,8,9) + 50 MVAR</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1044,30 +1060,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>60/30/60 MVA</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1103,37 +1120,42 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>KTSNO5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>KTSNO4</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>2x100 MVA (unit 1,4)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1166,34 +1188,35 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>10 MVAR</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1226,34 +1249,35 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>30/30/30 MVA</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1286,34 +1310,35 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>single busbar; 30/30/30 MVA</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1346,30 +1371,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>30/20/30 MVA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1402,34 +1428,35 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>ujung subsistem; drop tegangan</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_kediri12_ingest.xlsx
+++ b/samples/ss_kediri12_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_kediri12_ingest.xlsx
+++ b/samples/ss_kediri12_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Kediri 500/150 kV</t>
+          <t>IBT 1 Kediri 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,37 +734,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ngoro (bus 150 kV)</t>
+          <t>IBT 2 Kediri 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 NGORO7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NGORO7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>NGORO</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>4x60 MVA + 50 MVAR (bay 5 = MBL)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -778,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -795,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kediri (bus 150 kV)</t>
+          <t>Ngoro (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KDIRI5</t>
+          <t>NGORO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -809,7 +819,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -823,7 +833,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>injeksi 150 kV Kediri</t>
+          <t>4x60 MVA + 50 MVAR (bay 5 = MBL)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -835,14 +845,10 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -856,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jayakertas</t>
+          <t>Kediri (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JKTAS</t>
+          <t>KDIRI5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -870,7 +876,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -884,7 +890,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>T/L bay Kediri single phi</t>
+          <t>injeksi 150 kV Kediri</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -901,7 +907,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -917,12 +923,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kertosono (bus 150 kV)</t>
+          <t>Jayakertas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KTSNO5</t>
+          <t>JKTAS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -945,7 +951,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>150 kV Kertosono</t>
+          <t>T/L bay Kediri single phi</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -962,7 +968,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -978,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sukorejo (bus 150 kV)</t>
+          <t>Kertosono (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SKTIH5</t>
+          <t>KTSNO5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1006,7 +1012,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>60 MVA (bay 6,7,8,9) + 50 MVAR</t>
+          <t>150 kV Kertosono</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1018,10 +1024,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1035,12 +1045,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mojoagung</t>
+          <t>Sukorejo (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MJGNG</t>
+          <t>SKTIH5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1063,7 +1073,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60/30/60 MVA</t>
+          <t>60 MVA (bay 6,7,8,9) + 50 MVAR</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1092,49 +1102,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Kertosono</t>
+          <t>Mojoagung</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IBT 1 KTSNO5</t>
+          <t>MJGNG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>KTSNO5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KTSNO4</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2x100 MVA (unit 1,4)</t>
+          <t>60/30/60 MVA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1163,17 +1159,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kertosono (bus 70 kV)</t>
+          <t>IBT 150/70 kV Kertosono</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KTSNO4</t>
+          <t>IBT 1 KTSNO5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1181,17 +1177,31 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>KTSNO5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KTSNO4</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10 MVAR</t>
+          <t>2x100 MVA (unit 1,4)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1203,14 +1213,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1224,12 +1230,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nganjuk</t>
+          <t>Kertosono (bus 70 kV)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NGJUK</t>
+          <t>KTSNO4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1238,7 +1244,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1252,7 +1258,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30/30/30 MVA</t>
+          <t>10 MVAR</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1285,12 +1291,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caruban</t>
+          <t>Nganjuk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CRBAN</t>
+          <t>NGJUK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1299,7 +1305,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1313,7 +1319,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>single busbar; 30/30/30 MVA</t>
+          <t>30/30/30 MVA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1330,7 +1336,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1346,12 +1352,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ploso</t>
+          <t>Caruban</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PLOSO</t>
+          <t>CRBAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1360,7 +1366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1374,7 +1380,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30/20/30 MVA</t>
+          <t>single busbar; 30/30/30 MVA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1386,10 +1392,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1403,12 +1413,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagor</t>
+          <t>Ploso</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BAGOR</t>
+          <t>PLOSO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1417,7 +1427,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1431,7 +1441,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ujung subsistem; drop tegangan</t>
+          <t>30/20/30 MVA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1443,20 +1453,77 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bagor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BAGOR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ujung subsistem; drop tegangan</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2375,12 +2442,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Caruban hanya single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Caruban hanya single Busbar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2410,12 +2477,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Drop tegangan di ujungSubsistem Kediri 1,2</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di ujungSubsistem Kediri 1,2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
